--- a/tests/fixtures/05_expense_report/data-export-control.xlsx
+++ b/tests/fixtures/05_expense_report/data-export-control.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -593,355 +593,356 @@
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>exp.date</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>exp.description</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>exp.amount</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>exp.receipt</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D7" s="6" t="n">
         <v>46037</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Flight LHR-CDG</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>320</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>REC001</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D8" s="9" t="n">
         <v>46037</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Train CDG-Paris</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>REC002</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D9" s="6" t="n">
         <v>46038</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Taxi to hotel</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>REC003</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="11" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n">
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>exp.date</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>exp.description</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>exp.amount</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>exp.receipt</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D13" s="6" t="n">
         <v>46037</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Team lunch</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>REC004</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D14" s="9" t="n">
         <v>46038</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Client dinner</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>REC005</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D15" s="6" t="n">
         <v>46039</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Airport snacks</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>REC006</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n">
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n">
         <v>168.5</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>exp.date</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>exp.description</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>exp.amount</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>exp.receipt</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D19" s="6" t="n">
         <v>46037</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Hotel Paris night 1</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>REC007</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D20" s="9" t="n">
         <v>46038</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Hotel Paris night 2</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F20" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>REC008</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n">
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n">
         <v>390</v>
       </c>
     </row>
